--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2020_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2020_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:16</t>
+    <t xml:space="preserve">2026-09-24 01:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -684,7 +684,7 @@
         <v>0.02</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>-0.2</v>
@@ -707,7 +707,7 @@
         <v>0.04</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
@@ -730,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.17</v>
@@ -753,10 +753,10 @@
         <v>-0.05</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="12">
@@ -796,13 +796,13 @@
         <v>21</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="14">
@@ -822,7 +822,7 @@
         <v>-0.18</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>-0.12</v>
@@ -845,7 +845,7 @@
         <v>0.15</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.14</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2020_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2020_nuble.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:06</t>
+    <t xml:space="preserve">2026-10-01 23:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2020_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2020_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:18</t>
+    <t xml:space="preserve">2026-10-05 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
